--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$158</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5243" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5276" uniqueCount="636">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1025,8 +1025,22 @@
     <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this.resolve()}
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>Procedure.basedOn:tumorkonferenz</t>
+  </si>
+  <si>
+    <t>tumorkonferenz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-tumorkonferenz)
+</t>
   </si>
   <si>
     <t>Procedure.partOf</t>
@@ -2298,7 +2312,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK157"/>
+  <dimension ref="A1:AK158"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.44921875" customWidth="true" bestFit="true"/>
@@ -8114,7 +8128,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>319</v>
       </c>
@@ -8189,16 +8203,14 @@
         <v>74</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>319</v>
@@ -8213,7 +8225,7 @@
         <v>95</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>74</v>
@@ -8221,21 +8233,23 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="D57" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -8247,16 +8261,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8306,7 +8320,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8318,7 +8332,7 @@
         <v>95</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>74</v>
@@ -8326,42 +8340,42 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>74</v>
+        <v>331</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>159</v>
+        <v>332</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>10</v>
+        <v>333</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8387,13 +8401,13 @@
         <v>74</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>215</v>
+        <v>74</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>335</v>
+        <v>74</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>336</v>
+        <v>74</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -8411,62 +8425,62 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>96</v>
+        <v>326</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>338</v>
+        <v>74</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>339</v>
+        <v>10</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8492,13 +8506,13 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>149</v>
+        <v>215</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -8516,10 +8530,10 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>83</v>
@@ -8534,16 +8548,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>74</v>
+        <v>342</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8553,7 +8567,7 @@
         <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>74</v>
@@ -8565,13 +8579,13 @@
         <v>212</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8600,10 +8614,10 @@
         <v>149</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -8621,7 +8635,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8639,12 +8653,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8658,24 +8672,26 @@
         <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>99</v>
+        <v>349</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>74</v>
@@ -8700,13 +8716,13 @@
         <v>74</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>74</v>
+        <v>352</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>74</v>
+        <v>353</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -8724,7 +8740,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>101</v>
+        <v>348</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8733,10 +8749,10 @@
         <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>74</v>
@@ -8744,21 +8760,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -8770,17 +8786,15 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>74</v>
@@ -8817,31 +8831,31 @@
         <v>74</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>74</v>
@@ -8849,14 +8863,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8872,23 +8886,21 @@
         <v>74</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>224</v>
+        <v>105</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>225</v>
+        <v>106</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>74</v>
       </c>
@@ -8924,9 +8936,11 @@
         <v>74</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>74</v>
       </c>
@@ -8934,7 +8948,7 @@
         <v>110</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -8946,22 +8960,20 @@
         <v>95</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
@@ -8970,10 +8982,10 @@
         <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -8985,10 +8997,10 @@
         <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>356</v>
+        <v>224</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>357</v>
+        <v>225</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>226</v>
@@ -9004,7 +9016,7 @@
         <v>74</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>358</v>
+        <v>74</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>74</v>
@@ -9019,26 +9031,26 @@
         <v>74</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>359</v>
+        <v>74</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>228</v>
@@ -9059,14 +9071,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
@@ -9078,25 +9092,29 @@
         <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>99</v>
+        <v>360</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>74</v>
       </c>
@@ -9105,7 +9123,7 @@
         <v>74</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>74</v>
+        <v>362</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>74</v>
@@ -9120,13 +9138,11 @@
         <v>74</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>74</v>
+        <v>363</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -9144,19 +9160,19 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>74</v>
@@ -9164,21 +9180,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -9190,17 +9206,15 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>74</v>
@@ -9237,78 +9251,76 @@
         <v>74</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>74</v>
       </c>
@@ -9344,42 +9356,42 @@
         <v>74</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9387,13 +9399,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>74</v>
@@ -9402,18 +9414,20 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>74</v>
       </c>
@@ -9461,7 +9475,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -9479,12 +9493,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9492,13 +9506,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>74</v>
@@ -9507,20 +9521,18 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>74</v>
       </c>
@@ -9568,7 +9580,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9586,12 +9598,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9599,13 +9611,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>74</v>
@@ -9614,19 +9626,19 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>74</v>
@@ -9675,7 +9687,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9695,10 +9707,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9721,19 +9733,19 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>265</v>
+        <v>374</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>74</v>
@@ -9782,7 +9794,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -9802,10 +9814,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9828,19 +9840,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>74</v>
@@ -9889,7 +9901,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -9907,26 +9919,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>74</v>
@@ -9935,19 +9947,19 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>63</v>
+        <v>270</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>378</v>
+        <v>271</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>347</v>
+        <v>272</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>379</v>
+        <v>273</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>74</v>
@@ -9972,13 +9984,13 @@
         <v>74</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>380</v>
+        <v>74</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>381</v>
+        <v>74</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -9996,7 +10008,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>376</v>
+        <v>274</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -10008,50 +10020,54 @@
         <v>95</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>382</v>
+        <v>96</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>74</v>
+        <v>381</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>74</v>
       </c>
@@ -10075,13 +10091,13 @@
         <v>74</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>74</v>
+        <v>384</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>74</v>
+        <v>385</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>74</v>
@@ -10099,7 +10115,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>101</v>
+        <v>380</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -10108,10 +10124,10 @@
         <v>83</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>74</v>
+        <v>386</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>74</v>
@@ -10119,21 +10135,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>74</v>
@@ -10145,17 +10161,15 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>74</v>
@@ -10192,31 +10206,31 @@
         <v>74</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>74</v>
@@ -10224,46 +10238,44 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>224</v>
+        <v>105</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>225</v>
+        <v>106</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>74</v>
       </c>
@@ -10299,9 +10311,11 @@
         <v>74</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>74</v>
       </c>
@@ -10309,7 +10323,7 @@
         <v>110</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -10321,31 +10335,29 @@
         <v>95</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>84</v>
@@ -10357,16 +10369,16 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>388</v>
+        <v>137</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>389</v>
+        <v>224</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>390</v>
+        <v>225</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>391</v>
+        <v>226</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>227</v>
@@ -10379,7 +10391,7 @@
         <v>74</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>392</v>
+        <v>74</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>74</v>
@@ -10394,26 +10406,26 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>393</v>
+        <v>74</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>228</v>
@@ -10434,14 +10446,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
@@ -10453,25 +10467,29 @@
         <v>83</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>98</v>
+        <v>392</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>99</v>
+        <v>393</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>74</v>
       </c>
@@ -10480,7 +10498,7 @@
         <v>74</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>74</v>
+        <v>396</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>74</v>
@@ -10495,13 +10513,11 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>74</v>
+        <v>397</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -10519,19 +10535,19 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>74</v>
@@ -10539,21 +10555,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -10565,17 +10581,15 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>74</v>
@@ -10612,46 +10626,44 @@
         <v>74</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>103</v>
       </c>
@@ -10660,10 +10672,10 @@
         <v>75</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>74</v>
@@ -10672,13 +10684,13 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>400</v>
+        <v>104</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>401</v>
+        <v>105</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>402</v>
+        <v>106</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>107</v>
@@ -10719,16 +10731,16 @@
         <v>74</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>111</v>
@@ -10751,18 +10763,20 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C81" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="B81" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>83</v>
@@ -10774,29 +10788,27 @@
         <v>74</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>125</v>
+        <v>404</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>405</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>236</v>
+        <v>406</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>406</v>
+        <v>74</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>74</v>
@@ -10838,19 +10850,19 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>74</v>
@@ -10884,24 +10896,26 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>409</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>410</v>
+        <v>236</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>74</v>
+        <v>410</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>74</v>
@@ -10943,7 +10957,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
@@ -10989,20 +11003,18 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>413</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>250</v>
+        <v>414</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>74</v>
       </c>
@@ -11014,7 +11026,7 @@
         <v>74</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>414</v>
+        <v>74</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>74</v>
@@ -11050,7 +11062,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>75</v>
@@ -11062,18 +11074,18 @@
         <v>95</v>
       </c>
       <c r="AJ83" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AK83" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
+      <c r="B84" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11081,13 +11093,13 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>74</v>
@@ -11096,19 +11108,19 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>256</v>
+        <v>417</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>74</v>
@@ -11121,7 +11133,7 @@
         <v>74</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>74</v>
+        <v>418</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>74</v>
@@ -11157,7 +11169,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -11169,7 +11181,7 @@
         <v>95</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>96</v>
+        <v>419</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>74</v>
@@ -11177,10 +11189,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11203,19 +11215,19 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>265</v>
+        <v>374</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>74</v>
@@ -11264,7 +11276,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -11282,16 +11294,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
@@ -11303,7 +11313,7 @@
         <v>83</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>74</v>
@@ -11312,19 +11322,19 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>356</v>
+        <v>263</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>357</v>
+        <v>264</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>74</v>
@@ -11334,7 +11344,7 @@
         <v>74</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>358</v>
+        <v>74</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>74</v>
@@ -11349,11 +11359,13 @@
         <v>74</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>421</v>
+        <v>74</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>74</v>
@@ -11371,13 +11383,13 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>95</v>
@@ -11389,14 +11401,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
@@ -11408,25 +11422,29 @@
         <v>83</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>99</v>
+        <v>360</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>74</v>
       </c>
@@ -11435,7 +11453,7 @@
         <v>74</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>74</v>
+        <v>362</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>74</v>
@@ -11450,13 +11468,11 @@
         <v>74</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>74</v>
+        <v>425</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>74</v>
@@ -11474,19 +11490,19 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>74</v>
@@ -11494,21 +11510,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>74</v>
@@ -11520,17 +11536,15 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>74</v>
@@ -11567,78 +11581,76 @@
         <v>74</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>74</v>
       </c>
@@ -11674,39 +11686,39 @@
         <v>74</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>408</v>
@@ -11717,13 +11729,13 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>74</v>
@@ -11732,18 +11744,20 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>74</v>
       </c>
@@ -11791,7 +11805,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -11809,9 +11823,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>412</v>
@@ -11822,13 +11836,13 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>74</v>
@@ -11837,20 +11851,18 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>74</v>
       </c>
@@ -11898,7 +11910,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -11916,12 +11928,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11929,13 +11941,13 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>74</v>
@@ -11944,19 +11956,19 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>74</v>
@@ -12005,7 +12017,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
@@ -12025,10 +12037,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12051,19 +12063,19 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>265</v>
+        <v>374</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>74</v>
@@ -12112,7 +12124,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
@@ -12132,10 +12144,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12158,19 +12170,19 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>74</v>
@@ -12219,7 +12231,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -12237,26 +12249,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>431</v>
+        <v>74</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>74</v>
@@ -12265,18 +12277,20 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>432</v>
+        <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>433</v>
+        <v>270</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>434</v>
+        <v>271</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>74</v>
       </c>
@@ -12324,10 +12338,10 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>430</v>
+        <v>274</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>83</v>
@@ -12336,7 +12350,7 @@
         <v>95</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>325</v>
+        <v>96</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>74</v>
@@ -12344,18 +12358,18 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>74</v>
+        <v>435</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>83</v>
@@ -12379,7 +12393,7 @@
         <v>438</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>439</v>
+        <v>324</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12429,10 +12443,10 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>83</v>
@@ -12441,18 +12455,18 @@
         <v>95</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12460,7 +12474,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>83</v>
@@ -12475,16 +12489,16 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12522,17 +12536,19 @@
         <v>74</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AC97" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD97" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>446</v>
+        <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>75</v>
@@ -12544,7 +12560,7 @@
         <v>95</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>96</v>
+        <v>326</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>74</v>
@@ -12552,10 +12568,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12563,30 +12579,32 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>98</v>
+        <v>445</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>99</v>
+        <v>446</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>74</v>
@@ -12623,19 +12641,17 @@
         <v>74</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>74</v>
+        <v>450</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>101</v>
+        <v>444</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -12644,10 +12660,10 @@
         <v>83</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>74</v>
@@ -12655,21 +12671,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>74</v>
@@ -12681,17 +12697,15 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>74</v>
@@ -12728,31 +12742,31 @@
         <v>74</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>74</v>
@@ -12760,21 +12774,21 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>74</v>
@@ -12783,19 +12797,19 @@
         <v>74</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>450</v>
+        <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>451</v>
+        <v>105</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>452</v>
+        <v>106</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>453</v>
+        <v>107</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12833,42 +12847,42 @@
         <v>74</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>454</v>
+        <v>111</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>455</v>
+        <v>74</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>456</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12891,24 +12905,22 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q101" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
         <v>74</v>
       </c>
@@ -12952,7 +12964,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -12961,25 +12973,23 @@
         <v>83</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
@@ -13000,22 +13010,24 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q102" s="2"/>
+      <c r="Q102" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="R102" t="s" s="2">
         <v>74</v>
       </c>
@@ -13059,7 +13071,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -13068,13 +13080,13 @@
         <v>83</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>95</v>
+        <v>459</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>74</v>
+        <v>467</v>
       </c>
     </row>
     <row r="103" hidden="true">
@@ -13082,9 +13094,11 @@
         <v>468</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C103" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="D103" t="s" s="2">
         <v>74</v>
       </c>
@@ -13102,18 +13116,20 @@
         <v>74</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>98</v>
+        <v>445</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>99</v>
+        <v>470</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>74</v>
@@ -13162,7 +13178,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>101</v>
+        <v>444</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
@@ -13171,10 +13187,10 @@
         <v>83</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>74</v>
@@ -13182,21 +13198,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>74</v>
@@ -13208,17 +13224,15 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>74</v>
@@ -13255,74 +13269,74 @@
         <v>74</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>450</v>
+        <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>471</v>
+        <v>105</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>472</v>
+        <v>106</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>453</v>
+        <v>107</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -13360,31 +13374,31 @@
         <v>74</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>454</v>
+        <v>111</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>455</v>
+        <v>74</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>74</v>
@@ -13392,10 +13406,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13403,7 +13417,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>83</v>
@@ -13418,24 +13432,22 @@
         <v>84</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q106" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
         <v>74</v>
       </c>
@@ -13479,7 +13491,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -13488,7 +13500,7 @@
         <v>83</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>96</v>
@@ -13497,16 +13509,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>477</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>74</v>
       </c>
@@ -13518,7 +13528,7 @@
         <v>83</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>74</v>
@@ -13527,22 +13537,24 @@
         <v>84</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q107" s="2"/>
+      <c r="Q107" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="R107" t="s" s="2">
         <v>74</v>
       </c>
@@ -13586,7 +13598,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -13595,7 +13607,7 @@
         <v>83</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>95</v>
+        <v>459</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>96</v>
@@ -13609,9 +13621,11 @@
         <v>481</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="C108" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="D108" t="s" s="2">
         <v>74</v>
       </c>
@@ -13632,7 +13646,7 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>483</v>
@@ -13641,7 +13655,7 @@
         <v>484</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>324</v>
+        <v>448</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13691,7 +13705,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
@@ -13703,7 +13717,7 @@
         <v>95</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>325</v>
+        <v>96</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>74</v>
@@ -13737,13 +13751,13 @@
         <v>84</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>324</v>
@@ -13808,7 +13822,7 @@
         <v>95</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>74</v>
@@ -13816,10 +13830,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13830,7 +13844,7 @@
         <v>75</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>74</v>
@@ -13842,7 +13856,7 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="L110" t="s" s="2">
         <v>490</v>
@@ -13850,7 +13864,9 @@
       <c r="M110" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N110" s="2"/>
+      <c r="N110" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>74</v>
@@ -13899,19 +13915,19 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>96</v>
+        <v>326</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>74</v>
@@ -13933,7 +13949,7 @@
         <v>75</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>74</v>
@@ -13942,16 +13958,16 @@
         <v>74</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>98</v>
+        <v>493</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>99</v>
+        <v>494</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>100</v>
+        <v>495</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14002,19 +14018,19 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>101</v>
+        <v>492</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>74</v>
@@ -14022,21 +14038,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>74</v>
@@ -14048,17 +14064,15 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>74</v>
@@ -14095,31 +14109,31 @@
         <v>74</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>74</v>
@@ -14127,14 +14141,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>495</v>
+        <v>103</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -14147,26 +14161,24 @@
         <v>74</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>496</v>
+        <v>105</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>497</v>
+        <v>106</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O113" t="s" s="2">
-        <v>302</v>
-      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>74</v>
       </c>
@@ -14202,19 +14214,19 @@
         <v>74</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>498</v>
+        <v>111</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
@@ -14234,33 +14246,33 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>74</v>
+        <v>499</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="L114" t="s" s="2">
         <v>500</v>
@@ -14269,10 +14281,10 @@
         <v>501</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>347</v>
+        <v>107</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>502</v>
+        <v>302</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>74</v>
@@ -14297,13 +14309,13 @@
         <v>74</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>503</v>
+        <v>74</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>504</v>
+        <v>74</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>74</v>
@@ -14321,19 +14333,19 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>74</v>
@@ -14341,10 +14353,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14352,7 +14364,7 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>83</v>
@@ -14367,19 +14379,19 @@
         <v>84</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="O115" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>74</v>
@@ -14404,13 +14416,13 @@
         <v>74</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>74</v>
+        <v>507</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>74</v>
+        <v>508</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>74</v>
@@ -14428,10 +14440,10 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>83</v>
@@ -14440,7 +14452,7 @@
         <v>95</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>325</v>
+        <v>96</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>74</v>
@@ -14448,10 +14460,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14459,7 +14471,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>83</v>
@@ -14471,22 +14483,22 @@
         <v>74</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>324</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>74</v>
@@ -14535,10 +14547,10 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>83</v>
@@ -14547,7 +14559,7 @@
         <v>95</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>74</v>
@@ -14555,10 +14567,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14578,22 +14590,22 @@
         <v>74</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>324</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>74</v>
@@ -14642,7 +14654,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>75</v>
@@ -14654,7 +14666,7 @@
         <v>95</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>74</v>
@@ -14662,10 +14674,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14676,7 +14688,7 @@
         <v>75</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>74</v>
@@ -14688,7 +14700,7 @@
         <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>212</v>
+        <v>520</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>521</v>
@@ -14697,9 +14709,11 @@
         <v>522</v>
       </c>
       <c r="N118" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O118" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>74</v>
       </c>
@@ -14723,13 +14737,13 @@
         <v>74</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>524</v>
+        <v>74</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>525</v>
+        <v>74</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>74</v>
@@ -14747,30 +14761,30 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>96</v>
+        <v>326</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14784,7 +14798,7 @@
         <v>76</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>74</v>
@@ -14793,16 +14807,16 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N119" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -14828,13 +14842,13 @@
         <v>74</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>74</v>
+        <v>528</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>74</v>
+        <v>529</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>74</v>
@@ -14852,7 +14866,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>75</v>
@@ -14864,7 +14878,7 @@
         <v>95</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>325</v>
+        <v>96</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>74</v>
@@ -14872,10 +14886,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14898,7 +14912,7 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>212</v>
+        <v>531</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>532</v>
@@ -14933,13 +14947,13 @@
         <v>74</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>535</v>
+        <v>74</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>536</v>
+        <v>74</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>74</v>
@@ -14957,7 +14971,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>75</v>
@@ -14969,18 +14983,18 @@
         <v>95</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>96</v>
+        <v>326</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14991,27 +15005,29 @@
         <v>75</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>99</v>
+        <v>536</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>74</v>
@@ -15036,13 +15052,13 @@
         <v>74</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>74</v>
+        <v>539</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>74</v>
+        <v>540</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>74</v>
@@ -15060,19 +15076,19 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>101</v>
+        <v>535</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>74</v>
@@ -15080,21 +15096,21 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>74</v>
@@ -15106,17 +15122,15 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>74</v>
@@ -15153,31 +15167,31 @@
         <v>74</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>74</v>
@@ -15185,14 +15199,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -15202,29 +15216,27 @@
         <v>76</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>224</v>
+        <v>105</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>225</v>
+        <v>106</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>74</v>
       </c>
@@ -15260,9 +15272,11 @@
         <v>74</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AC123" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="AD123" t="s" s="2">
         <v>74</v>
       </c>
@@ -15270,7 +15284,7 @@
         <v>110</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>75</v>
@@ -15282,22 +15296,20 @@
         <v>95</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>542</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>74</v>
       </c>
@@ -15306,7 +15318,7 @@
         <v>75</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>84</v>
@@ -15321,10 +15333,10 @@
         <v>137</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>356</v>
+        <v>224</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>357</v>
+        <v>225</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>226</v>
@@ -15367,16 +15379,14 @@
         <v>74</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="AC124" s="2"/>
       <c r="AD124" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF124" t="s" s="2">
         <v>228</v>
@@ -15397,14 +15407,16 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="B125" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C125" s="2"/>
+      <c r="C125" t="s" s="2">
+        <v>546</v>
+      </c>
       <c r="D125" t="s" s="2">
         <v>74</v>
       </c>
@@ -15416,25 +15428,29 @@
         <v>83</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>99</v>
+        <v>360</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>74</v>
       </c>
@@ -15482,19 +15498,19 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>74</v>
@@ -15502,21 +15518,21 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>74</v>
@@ -15528,17 +15544,15 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>74</v>
@@ -15575,78 +15589,76 @@
         <v>74</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>74</v>
       </c>
@@ -15655,7 +15667,7 @@
         <v>74</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>549</v>
+        <v>74</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>74</v>
@@ -15682,31 +15694,31 @@
         <v>74</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>74</v>
@@ -15714,10 +15726,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15725,7 +15737,7 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>83</v>
@@ -15740,18 +15752,20 @@
         <v>84</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O128" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>74</v>
       </c>
@@ -15760,7 +15774,7 @@
         <v>74</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>74</v>
+        <v>553</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>74</v>
@@ -15799,7 +15813,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>75</v>
@@ -15819,10 +15833,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15830,7 +15844,7 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>83</v>
@@ -15845,20 +15859,18 @@
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>74</v>
       </c>
@@ -15906,7 +15918,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
@@ -15924,12 +15936,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15937,13 +15949,13 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>74</v>
@@ -15952,19 +15964,19 @@
         <v>84</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>74</v>
@@ -16013,7 +16025,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>75</v>
@@ -16033,10 +16045,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16059,19 +16071,19 @@
         <v>84</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>265</v>
+        <v>374</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>74</v>
@@ -16120,7 +16132,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>75</v>
@@ -16140,10 +16152,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16166,19 +16178,19 @@
         <v>84</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>74</v>
@@ -16227,7 +16239,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -16245,12 +16257,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16264,7 +16276,7 @@
         <v>83</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>74</v>
@@ -16273,18 +16285,20 @@
         <v>84</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>560</v>
+        <v>270</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>561</v>
+        <v>271</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>74</v>
       </c>
@@ -16308,13 +16322,13 @@
         <v>74</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>563</v>
+        <v>74</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>564</v>
+        <v>74</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>74</v>
@@ -16332,7 +16346,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>559</v>
+        <v>274</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
@@ -16350,12 +16364,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16369,24 +16383,26 @@
         <v>83</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>99</v>
+        <v>564</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N134" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>74</v>
@@ -16411,13 +16427,13 @@
         <v>74</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>74</v>
+        <v>567</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>74</v>
+        <v>568</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>74</v>
@@ -16435,7 +16451,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>101</v>
+        <v>563</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>75</v>
@@ -16444,10 +16460,10 @@
         <v>83</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>74</v>
@@ -16455,21 +16471,21 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>74</v>
@@ -16481,17 +16497,15 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>74</v>
@@ -16528,46 +16542,46 @@
         <v>74</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -16577,29 +16591,27 @@
         <v>76</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>568</v>
+        <v>105</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>569</v>
+        <v>106</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>74</v>
       </c>
@@ -16623,29 +16635,31 @@
         <v>74</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="Y136" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z136" t="s" s="2">
-        <v>570</v>
+        <v>74</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>75</v>
@@ -16657,13 +16671,13 @@
         <v>74</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
         <v>571</v>
       </c>
@@ -16679,28 +16693,32 @@
         <v>75</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>99</v>
+        <v>572</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
+        <v>573</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P137" t="s" s="2">
         <v>74</v>
       </c>
@@ -16724,13 +16742,11 @@
         <v>74</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>74</v>
+        <v>574</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>74</v>
@@ -16748,19 +16764,19 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>74</v>
@@ -16768,21 +16784,21 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>74</v>
@@ -16794,17 +16810,15 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>74</v>
@@ -16841,78 +16855,76 @@
         <v>74</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>74</v>
       </c>
@@ -16948,42 +16960,42 @@
         <v>74</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16997,7 +17009,7 @@
         <v>83</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>74</v>
@@ -17006,18 +17018,20 @@
         <v>84</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O140" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>74</v>
       </c>
@@ -17065,7 +17079,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>75</v>
@@ -17083,12 +17097,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17102,7 +17116,7 @@
         <v>83</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>74</v>
@@ -17111,18 +17125,18 @@
         <v>84</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>74</v>
       </c>
@@ -17170,7 +17184,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>75</v>
@@ -17185,15 +17199,15 @@
         <v>96</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>576</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="142" hidden="true">
+    <row r="142">
       <c r="A142" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17207,7 +17221,7 @@
         <v>83</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>74</v>
@@ -17216,17 +17230,17 @@
         <v>84</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>74</v>
@@ -17275,7 +17289,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>75</v>
@@ -17290,15 +17304,15 @@
         <v>96</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>74</v>
+        <v>580</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17321,19 +17335,17 @@
         <v>84</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>262</v>
+        <v>98</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>74</v>
@@ -17382,7 +17394,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>75</v>
@@ -17402,10 +17414,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17428,19 +17440,19 @@
         <v>84</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>74</v>
@@ -17489,7 +17501,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>75</v>
@@ -17509,10 +17521,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17523,7 +17535,7 @@
         <v>75</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>74</v>
@@ -17532,21 +17544,23 @@
         <v>74</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>581</v>
+        <v>98</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>582</v>
+        <v>270</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>583</v>
+        <v>271</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O145" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>74</v>
       </c>
@@ -17594,19 +17608,19 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>580</v>
+        <v>274</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>325</v>
+        <v>96</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>74</v>
@@ -17614,10 +17628,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17640,7 +17654,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>212</v>
+        <v>585</v>
       </c>
       <c r="L146" t="s" s="2">
         <v>586</v>
@@ -17675,13 +17689,13 @@
         <v>74</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>589</v>
+        <v>74</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>590</v>
+        <v>74</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>74</v>
@@ -17699,7 +17713,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>75</v>
@@ -17711,7 +17725,7 @@
         <v>95</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>96</v>
+        <v>326</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>74</v>
@@ -17719,10 +17733,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17745,20 +17759,18 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="L147" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>595</v>
-      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>74</v>
       </c>
@@ -17782,13 +17794,13 @@
         <v>74</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>74</v>
+        <v>593</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>74</v>
+        <v>594</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>74</v>
@@ -17806,7 +17818,7 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>75</v>
@@ -17818,7 +17830,7 @@
         <v>95</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>325</v>
+        <v>96</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>74</v>
@@ -17826,10 +17838,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17852,7 +17864,7 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>212</v>
+        <v>596</v>
       </c>
       <c r="L148" t="s" s="2">
         <v>597</v>
@@ -17861,9 +17873,11 @@
         <v>598</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O148" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>74</v>
       </c>
@@ -17887,13 +17901,13 @@
         <v>74</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>599</v>
+        <v>74</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>600</v>
+        <v>74</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -17911,7 +17925,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>75</v>
@@ -17923,18 +17937,18 @@
         <v>95</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>96</v>
+        <v>326</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17948,7 +17962,7 @@
         <v>76</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>74</v>
@@ -17957,16 +17971,16 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="L149" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="N149" t="s" s="2">
-        <v>605</v>
+        <v>351</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -17992,13 +18006,13 @@
         <v>74</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>74</v>
+        <v>603</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>74</v>
+        <v>604</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>74</v>
@@ -18016,7 +18030,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>75</v>
@@ -18034,12 +18048,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18053,7 +18067,7 @@
         <v>76</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>74</v>
@@ -18062,7 +18076,7 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>489</v>
+        <v>606</v>
       </c>
       <c r="L150" t="s" s="2">
         <v>607</v>
@@ -18070,7 +18084,9 @@
       <c r="M150" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="N150" s="2"/>
+      <c r="N150" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>74</v>
@@ -18119,7 +18135,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>75</v>
@@ -18139,10 +18155,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18153,7 +18169,7 @@
         <v>75</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>74</v>
@@ -18165,13 +18181,13 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>98</v>
+        <v>493</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>99</v>
+        <v>611</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>100</v>
+        <v>612</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -18222,19 +18238,19 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>101</v>
+        <v>610</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>74</v>
@@ -18242,21 +18258,21 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>74</v>
@@ -18268,17 +18284,15 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>74</v>
@@ -18315,31 +18329,31 @@
         <v>74</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>74</v>
@@ -18347,14 +18361,14 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>495</v>
+        <v>103</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -18367,26 +18381,24 @@
         <v>74</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>496</v>
+        <v>105</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>497</v>
+        <v>106</v>
       </c>
       <c r="N153" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O153" t="s" s="2">
-        <v>302</v>
-      </c>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>74</v>
       </c>
@@ -18422,19 +18434,19 @@
         <v>74</v>
       </c>
       <c r="AB153" t="s" s="2">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="AC153" t="s" s="2">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="AD153" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>498</v>
+        <v>111</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>75</v>
@@ -18454,44 +18466,46 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>74</v>
+        <v>499</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I154" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>613</v>
+        <v>500</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>614</v>
+        <v>501</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O154" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>74</v>
       </c>
@@ -18515,13 +18529,13 @@
         <v>74</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>615</v>
+        <v>74</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>616</v>
+        <v>74</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>74</v>
@@ -18539,19 +18553,19 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>612</v>
+        <v>502</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>74</v>
@@ -18559,10 +18573,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18570,7 +18584,7 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>83</v>
@@ -18585,16 +18599,16 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L155" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>620</v>
-      </c>
       <c r="N155" t="s" s="2">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -18620,13 +18634,13 @@
         <v>74</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>74</v>
+        <v>619</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>74</v>
+        <v>620</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>74</v>
@@ -18644,10 +18658,10 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>83</v>
@@ -18656,7 +18670,7 @@
         <v>95</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>325</v>
+        <v>96</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>74</v>
@@ -18675,10 +18689,10 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>74</v>
@@ -18699,11 +18713,9 @@
         <v>624</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>626</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>74</v>
       </c>
@@ -18754,16 +18766,16 @@
         <v>621</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>74</v>
@@ -18771,10 +18783,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18797,18 +18809,20 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>212</v>
+        <v>626</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="N157" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O157" s="2"/>
+      <c r="O157" t="s" s="2">
+        <v>630</v>
+      </c>
       <c r="P157" t="s" s="2">
         <v>74</v>
       </c>
@@ -18832,13 +18846,13 @@
         <v>74</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>630</v>
+        <v>74</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>631</v>
+        <v>74</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>74</v>
@@ -18856,7 +18870,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>75</v>
@@ -18868,14 +18882,119 @@
         <v>95</v>
       </c>
       <c r="AJ157" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="158" hidden="true">
+      <c r="A158" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="O158" s="2"/>
+      <c r="P158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AK157" t="s" s="2">
+      <c r="AK158" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK157">
+  <autoFilter ref="A1:AK158">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18885,7 +19004,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI156">
+  <conditionalFormatting sqref="A2:AI157">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$197</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7080" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7120" uniqueCount="764">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1477,6 +1477,9 @@
   </si>
   <si>
     <t>Procedure.code.coding.extension.value[x].code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
@@ -2081,6 +2084,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2682,7 +2701,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN196"/>
+  <dimension ref="A1:AN197"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -4984,7 +5003,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>115</v>
@@ -5210,7 +5229,7 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>99</v>
@@ -13516,7 +13535,7 @@
         <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>115</v>
@@ -13856,7 +13875,7 @@
         <v>79</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>115</v>
@@ -14080,7 +14099,7 @@
         <v>87</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>99</v>
@@ -14306,7 +14325,7 @@
         <v>79</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>115</v>
@@ -14422,7 +14441,7 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -14536,7 +14555,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -14590,7 +14609,9 @@
       <c r="M105" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N105" s="2"/>
+      <c r="N105" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="O105" t="s" s="2">
         <v>246</v>
       </c>
@@ -14650,7 +14671,7 @@
         <v>87</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>99</v>
@@ -14670,10 +14691,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14704,7 +14725,9 @@
       <c r="M106" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N106" s="2"/>
+      <c r="N106" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="O106" t="s" s="2">
         <v>253</v>
       </c>
@@ -14764,7 +14787,7 @@
         <v>87</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>99</v>
@@ -14784,10 +14807,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14880,7 +14903,7 @@
         <v>87</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>99</v>
@@ -14900,10 +14923,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14929,7 +14952,7 @@
         <v>128</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>229</v>
@@ -14945,7 +14968,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>77</v>
@@ -14996,7 +15019,7 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>99</v>
@@ -15016,10 +15039,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15045,10 +15068,10 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>239</v>
@@ -15110,7 +15133,7 @@
         <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>99</v>
@@ -15130,10 +15153,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15159,12 +15182,14 @@
         <v>162</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="N110" s="2"/>
+      <c r="N110" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="O110" t="s" s="2">
         <v>246</v>
       </c>
@@ -15179,7 +15204,7 @@
         <v>77</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>77</v>
@@ -15224,10 +15249,10 @@
         <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>77</v>
@@ -15244,10 +15269,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15278,7 +15303,9 @@
       <c r="M111" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N111" s="2"/>
+      <c r="N111" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="O111" t="s" s="2">
         <v>253</v>
       </c>
@@ -15338,7 +15365,7 @@
         <v>87</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>99</v>
@@ -15358,10 +15385,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15454,7 +15481,7 @@
         <v>87</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>99</v>
@@ -15474,7 +15501,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>434</v>
@@ -15543,7 +15570,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>77</v>
@@ -15590,7 +15617,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>443</v>
@@ -15702,7 +15729,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>445</v>
@@ -15816,10 +15843,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15932,10 +15959,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16046,10 +16073,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16160,10 +16187,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16274,10 +16301,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16390,10 +16417,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16506,14 +16533,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16532,13 +16559,13 @@
         <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16589,7 +16616,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>87</v>
@@ -16607,21 +16634,21 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16730,10 +16757,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16844,10 +16871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16873,13 +16900,13 @@
         <v>101</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16929,7 +16956,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16938,7 +16965,7 @@
         <v>87</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>99</v>
@@ -16958,10 +16985,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16987,13 +17014,13 @@
         <v>128</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17022,10 +17049,10 @@
         <v>144</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>77</v>
@@ -17043,7 +17070,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -17072,10 +17099,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17101,13 +17128,13 @@
         <v>341</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17157,7 +17184,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17186,10 +17213,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17215,13 +17242,13 @@
         <v>101</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -17271,7 +17298,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17300,10 +17327,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17326,16 +17353,16 @@
         <v>88</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17385,7 +17412,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -17403,21 +17430,21 @@
         <v>77</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17526,10 +17553,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17640,10 +17667,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17669,13 +17696,13 @@
         <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17725,7 +17752,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17734,7 +17761,7 @@
         <v>87</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>99</v>
@@ -17754,10 +17781,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17783,13 +17810,13 @@
         <v>128</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -17818,10 +17845,10 @@
         <v>144</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>77</v>
@@ -17839,7 +17866,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17868,10 +17895,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17897,13 +17924,13 @@
         <v>341</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17953,7 +17980,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17982,10 +18009,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18011,13 +18038,13 @@
         <v>101</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18067,7 +18094,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18096,10 +18123,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18122,16 +18149,16 @@
         <v>88</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -18169,17 +18196,17 @@
         <v>77</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AC136" s="2"/>
       <c r="AD136" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18197,21 +18224,21 @@
         <v>77</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18320,10 +18347,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18434,10 +18461,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18463,13 +18490,13 @@
         <v>206</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18519,7 +18546,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18528,13 +18555,13 @@
         <v>87</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>77</v>
@@ -18543,15 +18570,15 @@
         <v>77</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18577,20 +18604,20 @@
         <v>206</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q140" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="R140" t="s" s="2">
         <v>77</v>
@@ -18635,7 +18662,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18644,13 +18671,13 @@
         <v>87</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>77</v>
@@ -18659,18 +18686,18 @@
         <v>77</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>77</v>
@@ -18692,16 +18719,16 @@
         <v>88</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -18751,7 +18778,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18769,21 +18796,21 @@
         <v>77</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18892,10 +18919,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19006,10 +19033,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19035,13 +19062,13 @@
         <v>206</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19091,7 +19118,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -19100,7 +19127,7 @@
         <v>87</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>99</v>
@@ -19115,15 +19142,15 @@
         <v>77</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19149,20 +19176,20 @@
         <v>206</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q145" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="R145" t="s" s="2">
         <v>77</v>
@@ -19207,7 +19234,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19216,7 +19243,7 @@
         <v>87</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>99</v>
@@ -19231,18 +19258,18 @@
         <v>77</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>77</v>
@@ -19267,13 +19294,13 @@
         <v>206</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -19323,7 +19350,7 @@
         <v>77</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -19341,21 +19368,21 @@
         <v>77</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19378,13 +19405,13 @@
         <v>88</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19435,7 +19462,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19456,7 +19483,7 @@
         <v>77</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>77</v>
@@ -19464,10 +19491,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19490,13 +19517,13 @@
         <v>88</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -19547,7 +19574,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19568,7 +19595,7 @@
         <v>77</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>77</v>
@@ -19576,10 +19603,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19602,13 +19629,13 @@
         <v>88</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -19659,7 +19686,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19677,7 +19704,7 @@
         <v>77</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>77</v>
@@ -19688,10 +19715,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19800,10 +19827,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19914,14 +19941,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -19943,10 +19970,10 @@
         <v>107</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>110</v>
@@ -20001,7 +20028,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -20030,10 +20057,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20059,14 +20086,14 @@
         <v>275</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>77</v>
@@ -20094,10 +20121,10 @@
         <v>152</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>77</v>
@@ -20115,7 +20142,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -20133,21 +20160,21 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20170,17 +20197,17 @@
         <v>88</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>77</v>
@@ -20229,7 +20256,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>87</v>
@@ -20247,21 +20274,21 @@
         <v>77</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20284,17 +20311,17 @@
         <v>77</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>77</v>
@@ -20343,7 +20370,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -20372,10 +20399,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20398,17 +20425,17 @@
         <v>88</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>77</v>
@@ -20457,7 +20484,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20478,7 +20505,7 @@
         <v>77</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>77</v>
@@ -20486,10 +20513,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20515,13 +20542,13 @@
         <v>275</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20550,10 +20577,10 @@
         <v>152</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>77</v>
@@ -20571,7 +20598,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20589,10 +20616,10 @@
         <v>77</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>77</v>
@@ -20600,10 +20627,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20626,16 +20653,16 @@
         <v>88</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -20685,7 +20712,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20703,10 +20730,10 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>77</v>
@@ -20714,10 +20741,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20743,13 +20770,13 @@
         <v>275</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -20778,10 +20805,10 @@
         <v>152</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>77</v>
@@ -20799,7 +20826,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20823,15 +20850,15 @@
         <v>77</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20940,10 +20967,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21054,12 +21081,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="C162" s="2"/>
+      <c r="C162" t="s" s="2">
+        <v>667</v>
+      </c>
       <c r="D162" t="s" s="2">
         <v>77</v>
       </c>
@@ -21068,32 +21097,28 @@
         <v>78</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>140</v>
+        <v>668</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>281</v>
+        <v>669</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="N162" s="2"/>
+      <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>77</v>
       </c>
@@ -21129,17 +21154,19 @@
         <v>77</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AC162" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD162" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>285</v>
+        <v>114</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -21151,7 +21178,7 @@
         <v>77</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>77</v>
@@ -21163,19 +21190,17 @@
         <v>77</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="C163" t="s" s="2">
-        <v>668</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
         <v>77</v>
       </c>
@@ -21184,7 +21209,7 @@
         <v>78</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>88</v>
@@ -21199,10 +21224,10 @@
         <v>140</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>403</v>
+        <v>281</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>404</v>
+        <v>282</v>
       </c>
       <c r="N163" t="s" s="2">
         <v>283</v>
@@ -21245,16 +21270,14 @@
         <v>77</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="AC163" s="2"/>
       <c r="AD163" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF163" t="s" s="2">
         <v>285</v>
@@ -21284,14 +21307,16 @@
         <v>286</v>
       </c>
     </row>
-    <row r="164" hidden="true">
+    <row r="164">
       <c r="A164" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C164" s="2"/>
+        <v>671</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>674</v>
+      </c>
       <c r="D164" t="s" s="2">
         <v>77</v>
       </c>
@@ -21303,25 +21328,29 @@
         <v>87</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>102</v>
+        <v>403</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
       </c>
@@ -21369,19 +21398,19 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI164" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>77</v>
@@ -21393,26 +21422,26 @@
         <v>77</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>77</v>
@@ -21424,17 +21453,15 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>77</v>
@@ -21471,31 +21498,31 @@
         <v>77</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC165" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD165" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>77</v>
@@ -21510,48 +21537,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>77</v>
       </c>
@@ -21560,7 +21585,7 @@
         <v>77</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>77</v>
@@ -21587,31 +21612,31 @@
         <v>77</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>77</v>
@@ -21623,15 +21648,15 @@
         <v>77</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21639,7 +21664,7 @@
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G167" t="s" s="2">
         <v>87</v>
@@ -21654,18 +21679,20 @@
         <v>88</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O167" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O167" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P167" t="s" s="2">
         <v>77</v>
       </c>
@@ -21674,7 +21701,7 @@
         <v>77</v>
       </c>
       <c r="S167" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="T167" t="s" s="2">
         <v>77</v>
@@ -21713,7 +21740,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21737,15 +21764,15 @@
         <v>77</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21753,7 +21780,7 @@
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G168" t="s" s="2">
         <v>87</v>
@@ -21768,18 +21795,18 @@
         <v>88</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N168" s="2"/>
-      <c r="O168" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>77</v>
       </c>
@@ -21827,7 +21854,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21851,15 +21878,15 @@
         <v>77</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="169" hidden="true">
+    <row r="169">
       <c r="A169" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21867,13 +21894,13 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G169" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>77</v>
@@ -21882,17 +21909,17 @@
         <v>88</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -21941,7 +21968,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21965,15 +21992,15 @@
         <v>77</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -21996,19 +22023,17 @@
         <v>88</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
@@ -22057,7 +22082,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>78</v>
@@ -22081,15 +22106,15 @@
         <v>77</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22112,19 +22137,19 @@
         <v>88</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>77</v>
@@ -22173,7 +22198,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -22197,15 +22222,15 @@
         <v>77</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22219,7 +22244,7 @@
         <v>87</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>77</v>
@@ -22228,18 +22253,20 @@
         <v>88</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>275</v>
+        <v>101</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>685</v>
+        <v>305</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>686</v>
+        <v>306</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="O172" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P172" t="s" s="2">
         <v>77</v>
       </c>
@@ -22263,13 +22290,13 @@
         <v>77</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>688</v>
+        <v>77</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>689</v>
+        <v>77</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>77</v>
@@ -22287,7 +22314,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>684</v>
+        <v>309</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22311,10 +22338,10 @@
         <v>77</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>77</v>
+        <v>310</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
         <v>690</v>
       </c>
@@ -22333,24 +22360,26 @@
         <v>87</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>102</v>
+        <v>691</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N173" s="2"/>
+        <v>692</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>693</v>
+      </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>77</v>
@@ -22375,13 +22404,13 @@
         <v>77</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>77</v>
+        <v>694</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>77</v>
+        <v>695</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>77</v>
@@ -22399,7 +22428,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>104</v>
+        <v>690</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -22411,7 +22440,7 @@
         <v>77</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>77</v>
@@ -22428,21 +22457,21 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>77</v>
@@ -22454,17 +22483,15 @@
         <v>77</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>77</v>
@@ -22501,31 +22528,31 @@
         <v>77</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC174" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD174" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI174" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>77</v>
@@ -22540,16 +22567,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -22559,29 +22586,27 @@
         <v>79</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>693</v>
+        <v>108</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>694</v>
+        <v>109</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>77</v>
       </c>
@@ -22605,29 +22630,31 @@
         <v>77</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y175" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z175" t="s" s="2">
-        <v>695</v>
+        <v>77</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>285</v>
+        <v>114</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>78</v>
@@ -22639,7 +22666,7 @@
         <v>77</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>77</v>
@@ -22651,15 +22678,15 @@
         <v>77</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="176" hidden="true">
+    <row r="176">
       <c r="A176" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22670,28 +22697,32 @@
         <v>78</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I176" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>102</v>
+        <v>699</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N176" s="2"/>
-      <c r="O176" s="2"/>
+        <v>700</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>77</v>
       </c>
@@ -22715,13 +22746,11 @@
         <v>77</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y176" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>77</v>
+        <v>701</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>77</v>
@@ -22739,19 +22768,19 @@
         <v>77</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>77</v>
@@ -22763,26 +22792,26 @@
         <v>77</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>77</v>
@@ -22794,17 +22823,15 @@
         <v>77</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -22841,31 +22868,31 @@
         <v>77</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>77</v>
@@ -22880,48 +22907,46 @@
         <v>77</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I178" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>77</v>
       </c>
@@ -22957,31 +22982,31 @@
         <v>77</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AC178" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AD178" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>77</v>
@@ -22993,15 +23018,15 @@
         <v>77</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23015,7 +23040,7 @@
         <v>87</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>77</v>
@@ -23024,18 +23049,20 @@
         <v>88</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O179" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="O179" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
       </c>
@@ -23083,7 +23110,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
@@ -23107,15 +23134,15 @@
         <v>77</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23129,7 +23156,7 @@
         <v>87</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>77</v>
@@ -23138,18 +23165,18 @@
         <v>88</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N180" s="2"/>
-      <c r="O180" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>77</v>
       </c>
@@ -23197,7 +23224,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -23212,7 +23239,7 @@
         <v>99</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>701</v>
+        <v>77</v>
       </c>
       <c r="AL180" t="s" s="2">
         <v>77</v>
@@ -23221,15 +23248,15 @@
         <v>77</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="181" hidden="true">
+    <row r="181">
       <c r="A181" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23243,7 +23270,7 @@
         <v>87</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>77</v>
@@ -23252,17 +23279,17 @@
         <v>88</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>77</v>
@@ -23311,7 +23338,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>78</v>
@@ -23326,7 +23353,7 @@
         <v>99</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>77</v>
+        <v>707</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>77</v>
@@ -23335,15 +23362,15 @@
         <v>77</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23366,19 +23393,17 @@
         <v>88</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N182" s="2"/>
       <c r="O182" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>77</v>
@@ -23427,7 +23452,7 @@
         <v>77</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>78</v>
@@ -23451,15 +23476,15 @@
         <v>77</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23482,19 +23507,19 @@
         <v>88</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>77</v>
@@ -23543,7 +23568,7 @@
         <v>77</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>78</v>
@@ -23567,15 +23592,15 @@
         <v>77</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>310</v>
+        <v>264</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23586,7 +23611,7 @@
         <v>78</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>77</v>
@@ -23595,21 +23620,23 @@
         <v>77</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>706</v>
+        <v>101</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>707</v>
+        <v>305</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>708</v>
+        <v>306</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="O184" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P184" t="s" s="2">
         <v>77</v>
       </c>
@@ -23657,13 +23684,13 @@
         <v>77</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>705</v>
+        <v>309</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>77</v>
@@ -23681,15 +23708,15 @@
         <v>77</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>77</v>
+        <v>310</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23712,16 +23739,16 @@
         <v>77</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>275</v>
+        <v>712</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -23747,13 +23774,13 @@
         <v>77</v>
       </c>
       <c r="X185" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>714</v>
+        <v>77</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>715</v>
+        <v>77</v>
       </c>
       <c r="AA185" t="s" s="2">
         <v>77</v>
@@ -23771,7 +23798,7 @@
         <v>77</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>78</v>
@@ -23826,18 +23853,18 @@
         <v>77</v>
       </c>
       <c r="K186" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L186" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="L186" t="s" s="2">
+      <c r="M186" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="N186" s="2"/>
-      <c r="O186" t="s" s="2">
-        <v>720</v>
-      </c>
+      <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
         <v>77</v>
       </c>
@@ -23861,13 +23888,13 @@
         <v>77</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>77</v>
+        <v>720</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>77</v>
+        <v>721</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>77</v>
@@ -23914,10 +23941,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23940,16 +23967,18 @@
         <v>77</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>275</v>
+        <v>723</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="N187" s="2"/>
-      <c r="O187" s="2"/>
+      <c r="O187" t="s" s="2">
+        <v>726</v>
+      </c>
       <c r="P187" t="s" s="2">
         <v>77</v>
       </c>
@@ -23973,13 +24002,13 @@
         <v>77</v>
       </c>
       <c r="X187" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y187" t="s" s="2">
-        <v>724</v>
+        <v>77</v>
       </c>
       <c r="Z187" t="s" s="2">
-        <v>725</v>
+        <v>77</v>
       </c>
       <c r="AA187" t="s" s="2">
         <v>77</v>
@@ -23997,7 +24026,7 @@
         <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>78</v>
@@ -24024,12 +24053,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24043,7 +24072,7 @@
         <v>79</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>77</v>
@@ -24052,7 +24081,7 @@
         <v>77</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>727</v>
+        <v>275</v>
       </c>
       <c r="L188" t="s" s="2">
         <v>728</v>
@@ -24085,13 +24114,13 @@
         <v>77</v>
       </c>
       <c r="X188" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y188" t="s" s="2">
-        <v>77</v>
+        <v>730</v>
       </c>
       <c r="Z188" t="s" s="2">
-        <v>77</v>
+        <v>731</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>77</v>
@@ -24109,7 +24138,7 @@
         <v>77</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>78</v>
@@ -24127,16 +24156,16 @@
         <v>77</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>730</v>
+        <v>77</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>731</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="189" hidden="true">
+    <row r="189">
       <c r="A189" t="s" s="2">
         <v>732</v>
       </c>
@@ -24155,7 +24184,7 @@
         <v>79</v>
       </c>
       <c r="H189" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I189" t="s" s="2">
         <v>77</v>
@@ -24164,13 +24193,13 @@
         <v>77</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>604</v>
+        <v>733</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -24239,21 +24268,21 @@
         <v>77</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>77</v>
+        <v>736</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>77</v>
+        <v>737</v>
       </c>
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24264,7 +24293,7 @@
         <v>78</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>77</v>
@@ -24276,13 +24305,13 @@
         <v>77</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>101</v>
+        <v>605</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>102</v>
+        <v>739</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>103</v>
+        <v>740</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -24333,19 +24362,19 @@
         <v>77</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>104</v>
+        <v>738</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK190" t="s" s="2">
         <v>77</v>
@@ -24362,21 +24391,21 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>77</v>
@@ -24388,17 +24417,15 @@
         <v>77</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>110</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N191" s="2"/>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>77</v>
@@ -24447,19 +24474,19 @@
         <v>77</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>77</v>
@@ -24476,14 +24503,14 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>611</v>
+        <v>106</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
@@ -24496,26 +24523,24 @@
         <v>77</v>
       </c>
       <c r="I192" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J192" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K192" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>612</v>
+        <v>108</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>613</v>
+        <v>109</v>
       </c>
       <c r="N192" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="O192" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>77</v>
       </c>
@@ -24563,7 +24588,7 @@
         <v>77</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>614</v>
+        <v>114</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>78</v>
@@ -24592,42 +24617,46 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>77</v>
+        <v>612</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I193" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>275</v>
+        <v>107</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>739</v>
+        <v>613</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="N193" s="2"/>
-      <c r="O193" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P193" t="s" s="2">
         <v>77</v>
       </c>
@@ -24651,13 +24680,13 @@
         <v>77</v>
       </c>
       <c r="X193" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="Y193" t="s" s="2">
-        <v>741</v>
+        <v>77</v>
       </c>
       <c r="Z193" t="s" s="2">
-        <v>742</v>
+        <v>77</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>77</v>
@@ -24675,19 +24704,19 @@
         <v>77</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>738</v>
+        <v>615</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>77</v>
@@ -24704,10 +24733,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24715,7 +24744,7 @@
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G194" t="s" s="2">
         <v>87</v>
@@ -24730,7 +24759,7 @@
         <v>77</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>744</v>
+        <v>275</v>
       </c>
       <c r="L194" t="s" s="2">
         <v>745</v>
@@ -24763,13 +24792,13 @@
         <v>77</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>77</v>
+        <v>747</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>77</v>
+        <v>748</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>77</v>
@@ -24787,10 +24816,10 @@
         <v>77</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>87</v>
@@ -24816,10 +24845,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24827,10 +24856,10 @@
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>77</v>
@@ -24842,20 +24871,16 @@
         <v>77</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="O195" t="s" s="2">
         <v>752</v>
       </c>
+      <c r="N195" s="2"/>
+      <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>77</v>
       </c>
@@ -24903,13 +24928,13 @@
         <v>77</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>77</v>
@@ -24958,18 +24983,20 @@
         <v>77</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>275</v>
+        <v>754</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="O196" s="2"/>
+        <v>757</v>
+      </c>
+      <c r="O196" t="s" s="2">
+        <v>758</v>
+      </c>
       <c r="P196" t="s" s="2">
         <v>77</v>
       </c>
@@ -24993,13 +25020,13 @@
         <v>77</v>
       </c>
       <c r="X196" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Y196" t="s" s="2">
-        <v>756</v>
+        <v>77</v>
       </c>
       <c r="Z196" t="s" s="2">
-        <v>757</v>
+        <v>77</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>77</v>
@@ -25044,8 +25071,122 @@
         <v>77</v>
       </c>
     </row>
+    <row r="197" hidden="true">
+      <c r="A197" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C197" s="2"/>
+      <c r="D197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E197" s="2"/>
+      <c r="F197" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G197" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K197" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L197" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="M197" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="N197" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="O197" s="2"/>
+      <c r="P197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q197" s="2"/>
+      <c r="R197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X197" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Y197" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="Z197" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AA197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF197" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AG197" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH197" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ197" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM197" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN197" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AN196">
+  <autoFilter ref="A1:AN197">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -25055,7 +25196,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI195">
+  <conditionalFormatting sqref="A2:AI196">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-strahlentherapie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
